--- a/ValueSet-HIV.B.DE15.xlsx
+++ b/ValueSet-HIV.B.DE15.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-06T17:04:54+00:00</t>
+    <t>2024-08-15T18:29:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE15.xlsx
+++ b/ValueSet-HIV.B.DE15.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-15T18:29:29+00:00</t>
+    <t>2024-08-15T19:00:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE15.xlsx
+++ b/ValueSet-HIV.B.DE15.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-15T19:00:48+00:00</t>
+    <t>2024-08-15T19:04:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
